--- a/skills/mom-business-data-generator/templates/产品与工艺_模板.xlsx
+++ b/skills/mom-business-data-generator/templates/产品与工艺_模板.xlsx
@@ -16,12 +16,13 @@
     <sheet name="工艺路线工序序列" r:id="rId10" sheetId="8"/>
     <sheet name="工艺路线工序物料" r:id="rId11" sheetId="9"/>
     <sheet name="工艺路线工步" r:id="rId12" sheetId="10"/>
+    <sheet name="工艺路线与资质等级关系" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10506" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10910" uniqueCount="79">
   <si>
     <t>填写说明</t>
   </si>
@@ -32,6 +33,7 @@
 4、引用属性如果是包含版本号，则版本号必填。
 5、工艺路线导入时，请确保每次导入的都是一整套工艺数据，包括工艺路线信息、工艺工序信息以及工序序列关系信息。
 6、【工艺路线工序序列】sheet页中，若不存在上道工序，则无需填写工序序列。
+7、【工艺路线资质】sheet页为可选项，如需绑定工序资质等级，请按格式填写。
 </t>
   </si>
   <si>
@@ -101,12 +103,6 @@
     <t>物料阶段</t>
   </si>
   <si>
-    <t>发布版本时间</t>
-  </si>
-  <si>
-    <t>发布人</t>
-  </si>
-  <si>
     <t>*版本号</t>
   </si>
   <si>
@@ -117,6 +113,15 @@
   </si>
   <si>
     <t>*密级</t>
+  </si>
+  <si>
+    <t>集成系统</t>
+  </si>
+  <si>
+    <t>集成数据主键</t>
+  </si>
+  <si>
+    <t>集成创建时间</t>
   </si>
   <si>
     <t>*物料版本号</t>
@@ -138,12 +143,6 @@
   </si>
   <si>
     <t>父物料版本</t>
-  </si>
-  <si>
-    <t>*MBOM版本号</t>
-  </si>
-  <si>
-    <t>*MBOM编码</t>
   </si>
   <si>
     <t>物料名称</t>
@@ -177,6 +176,12 @@
   </si>
   <si>
     <t>引用物料编码</t>
+  </si>
+  <si>
+    <t>*MBom版本号</t>
+  </si>
+  <si>
+    <t>*MBom编码</t>
   </si>
   <si>
     <t>*工艺类型</t>
@@ -259,13 +264,16 @@
   <si>
     <t>工步内容</t>
   </si>
+  <si>
+    <t>*资质等级编码</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -282,6 +290,18 @@
     <font>
       <name val="Calibri"/>
       <sz val="12.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -450,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -539,6 +559,15 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyAlignment="true" applyBorder="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="true" applyAlignment="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -581,22 +610,22 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="28">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s" s="28">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s" s="27">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s" s="27">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" t="s" s="27">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F1" t="s" s="27">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
@@ -2596,6 +2625,1436 @@
         <v>3</v>
       </c>
       <c r="F101" s="29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D101"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="10.0" customWidth="true"/>
+    <col min="2" max="2" width="13.0" customWidth="true"/>
+    <col min="3" max="3" width="14.0" customWidth="true"/>
+    <col min="4" max="4" width="13.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.0" customHeight="true">
+      <c r="A1" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s" s="31">
+        <v>78</v>
+      </c>
+      <c r="C1" t="s" s="31">
+        <v>68</v>
+      </c>
+      <c r="D1" t="s" s="31">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D53" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D73" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C81" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C83" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C85" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C87" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C88" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C89" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C90" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C91" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C93" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C94" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D96" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C98" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="32" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2606,7 +4065,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AA101"/>
+  <dimension ref="A1:AB101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="11.0" customWidth="true"/>
@@ -2630,12 +4089,13 @@
     <col min="19" max="19" width="13.0" customWidth="true"/>
     <col min="20" max="20" width="12.0" customWidth="true"/>
     <col min="21" max="21" width="10.0" customWidth="true"/>
-    <col min="22" max="22" width="12.0" customWidth="true"/>
+    <col min="22" max="22" width="10.0" customWidth="true"/>
     <col min="23" max="23" width="9.0" customWidth="true"/>
-    <col min="24" max="24" width="10.0" customWidth="true"/>
+    <col min="24" max="24" width="8.0" customWidth="true"/>
     <col min="25" max="25" width="9.0" customWidth="true"/>
-    <col min="26" max="26" width="8.0" customWidth="true"/>
-    <col min="27" max="27" width="9.0" customWidth="true"/>
+    <col min="26" max="26" width="10.0" customWidth="true"/>
+    <col min="27" max="27" width="12.0" customWidth="true"/>
+    <col min="28" max="28" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
@@ -2705,7 +4165,7 @@
       <c r="V1" t="s" s="3">
         <v>24</v>
       </c>
-      <c r="W1" t="s" s="4">
+      <c r="W1" t="s" s="3">
         <v>25</v>
       </c>
       <c r="X1" t="s" s="3">
@@ -2720,6 +4180,9 @@
       <c r="AA1" t="s" s="3">
         <v>29</v>
       </c>
+      <c r="AB1" t="s" s="3">
+        <v>30</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
@@ -2803,6 +4266,9 @@
       <c r="AA2" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB2" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
@@ -2886,6 +4352,9 @@
       <c r="AA3" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB3" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
@@ -2969,6 +4438,9 @@
       <c r="AA4" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB4" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
@@ -3052,6 +4524,9 @@
       <c r="AA5" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB5" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
@@ -3135,6 +4610,9 @@
       <c r="AA6" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB6" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
@@ -3218,6 +4696,9 @@
       <c r="AA7" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB7" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
@@ -3301,6 +4782,9 @@
       <c r="AA8" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB8" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
@@ -3384,6 +4868,9 @@
       <c r="AA9" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB9" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
@@ -3467,6 +4954,9 @@
       <c r="AA10" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB10" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
@@ -3550,6 +5040,9 @@
       <c r="AA11" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB11" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
@@ -3633,6 +5126,9 @@
       <c r="AA12" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB12" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
@@ -3716,6 +5212,9 @@
       <c r="AA13" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB13" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
@@ -3799,6 +5298,9 @@
       <c r="AA14" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB14" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
@@ -3882,6 +5384,9 @@
       <c r="AA15" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB15" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
@@ -3965,6 +5470,9 @@
       <c r="AA16" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB16" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
@@ -4048,6 +5556,9 @@
       <c r="AA17" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB17" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
@@ -4131,6 +5642,9 @@
       <c r="AA18" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB18" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
@@ -4214,6 +5728,9 @@
       <c r="AA19" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB19" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
@@ -4297,6 +5814,9 @@
       <c r="AA20" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB20" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
@@ -4380,6 +5900,9 @@
       <c r="AA21" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB21" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
@@ -4463,6 +5986,9 @@
       <c r="AA22" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB22" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
@@ -4546,6 +6072,9 @@
       <c r="AA23" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB23" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
@@ -4629,6 +6158,9 @@
       <c r="AA24" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB24" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
@@ -4712,6 +6244,9 @@
       <c r="AA25" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB25" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
@@ -4795,6 +6330,9 @@
       <c r="AA26" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB26" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
@@ -4878,6 +6416,9 @@
       <c r="AA27" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB27" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
@@ -4961,6 +6502,9 @@
       <c r="AA28" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB28" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
@@ -5044,6 +6588,9 @@
       <c r="AA29" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB29" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
@@ -5127,6 +6674,9 @@
       <c r="AA30" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB30" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
@@ -5210,6 +6760,9 @@
       <c r="AA31" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB31" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
@@ -5293,6 +6846,9 @@
       <c r="AA32" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB32" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
@@ -5376,6 +6932,9 @@
       <c r="AA33" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB33" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
@@ -5459,6 +7018,9 @@
       <c r="AA34" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB34" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
@@ -5542,6 +7104,9 @@
       <c r="AA35" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB35" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
@@ -5625,6 +7190,9 @@
       <c r="AA36" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB36" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
@@ -5708,6 +7276,9 @@
       <c r="AA37" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB37" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
@@ -5791,6 +7362,9 @@
       <c r="AA38" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB38" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
@@ -5874,6 +7448,9 @@
       <c r="AA39" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB39" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
@@ -5957,6 +7534,9 @@
       <c r="AA40" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB40" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
@@ -6040,6 +7620,9 @@
       <c r="AA41" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB41" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
@@ -6123,6 +7706,9 @@
       <c r="AA42" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB42" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
@@ -6206,6 +7792,9 @@
       <c r="AA43" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB43" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
@@ -6289,6 +7878,9 @@
       <c r="AA44" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB44" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
@@ -6372,6 +7964,9 @@
       <c r="AA45" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB45" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
@@ -6455,6 +8050,9 @@
       <c r="AA46" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB46" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
@@ -6538,6 +8136,9 @@
       <c r="AA47" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB47" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
@@ -6621,6 +8222,9 @@
       <c r="AA48" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB48" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
@@ -6704,6 +8308,9 @@
       <c r="AA49" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB49" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
@@ -6787,6 +8394,9 @@
       <c r="AA50" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB50" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
@@ -6870,6 +8480,9 @@
       <c r="AA51" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB51" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
@@ -6953,6 +8566,9 @@
       <c r="AA52" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB52" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
@@ -7036,6 +8652,9 @@
       <c r="AA53" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB53" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
@@ -7119,6 +8738,9 @@
       <c r="AA54" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB54" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
@@ -7202,6 +8824,9 @@
       <c r="AA55" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB55" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
@@ -7285,6 +8910,9 @@
       <c r="AA56" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB56" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
@@ -7368,6 +8996,9 @@
       <c r="AA57" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB57" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
@@ -7451,6 +9082,9 @@
       <c r="AA58" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB58" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
@@ -7534,6 +9168,9 @@
       <c r="AA59" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB59" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
@@ -7617,6 +9254,9 @@
       <c r="AA60" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB60" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
@@ -7700,6 +9340,9 @@
       <c r="AA61" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB61" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
@@ -7783,6 +9426,9 @@
       <c r="AA62" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB62" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
@@ -7866,6 +9512,9 @@
       <c r="AA63" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB63" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
@@ -7949,6 +9598,9 @@
       <c r="AA64" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB64" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="s">
@@ -8032,6 +9684,9 @@
       <c r="AA65" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB65" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="s">
@@ -8115,6 +9770,9 @@
       <c r="AA66" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB66" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="s">
@@ -8198,6 +9856,9 @@
       <c r="AA67" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB67" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
@@ -8281,6 +9942,9 @@
       <c r="AA68" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB68" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
@@ -8364,6 +10028,9 @@
       <c r="AA69" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB69" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
@@ -8447,6 +10114,9 @@
       <c r="AA70" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB70" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
@@ -8530,6 +10200,9 @@
       <c r="AA71" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB71" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
@@ -8613,6 +10286,9 @@
       <c r="AA72" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB72" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
@@ -8696,6 +10372,9 @@
       <c r="AA73" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB73" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="s">
@@ -8779,6 +10458,9 @@
       <c r="AA74" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB74" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="s">
@@ -8862,6 +10544,9 @@
       <c r="AA75" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB75" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="s">
@@ -8945,6 +10630,9 @@
       <c r="AA76" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB76" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
@@ -9028,6 +10716,9 @@
       <c r="AA77" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB77" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
@@ -9111,6 +10802,9 @@
       <c r="AA78" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB78" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="s">
@@ -9194,6 +10888,9 @@
       <c r="AA79" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB79" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="s">
@@ -9277,6 +10974,9 @@
       <c r="AA80" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB80" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="s">
@@ -9360,6 +11060,9 @@
       <c r="AA81" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB81" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
@@ -9443,6 +11146,9 @@
       <c r="AA82" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB82" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
@@ -9526,6 +11232,9 @@
       <c r="AA83" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB83" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="s">
@@ -9609,6 +11318,9 @@
       <c r="AA84" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB84" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
@@ -9692,6 +11404,9 @@
       <c r="AA85" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB85" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="s">
@@ -9775,6 +11490,9 @@
       <c r="AA86" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB86" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="s">
@@ -9858,6 +11576,9 @@
       <c r="AA87" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB87" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
@@ -9941,6 +11662,9 @@
       <c r="AA88" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB88" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
@@ -10024,6 +11748,9 @@
       <c r="AA89" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB89" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="s">
@@ -10107,6 +11834,9 @@
       <c r="AA90" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB90" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="s">
@@ -10190,6 +11920,9 @@
       <c r="AA91" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB91" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
@@ -10273,6 +12006,9 @@
       <c r="AA92" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB92" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
@@ -10356,6 +12092,9 @@
       <c r="AA93" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB93" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
@@ -10439,6 +12178,9 @@
       <c r="AA94" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB94" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
@@ -10522,6 +12264,9 @@
       <c r="AA95" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB95" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
@@ -10605,6 +12350,9 @@
       <c r="AA96" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB96" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
@@ -10688,6 +12436,9 @@
       <c r="AA97" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB97" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
@@ -10771,6 +12522,9 @@
       <c r="AA98" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB98" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
@@ -10854,6 +12608,9 @@
       <c r="AA99" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB99" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
@@ -10937,6 +12694,9 @@
       <c r="AA100" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="AB100" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
@@ -11018,6 +12778,9 @@
         <v>3</v>
       </c>
       <c r="AA101" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB101" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -11053,7 +12816,7 @@
     <dataValidation type="list" sqref="T2:T101" allowBlank="true" errorStyle="stop">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AA2:AA101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="Y2:Y101" allowBlank="true" errorStyle="stop">
       <formula1>"公开,内部,秘密,机密"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11074,16 +12837,16 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s" s="6">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
@@ -12493,31 +14256,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
     <col min="2" max="2" width="11.0" customWidth="true"/>
-    <col min="3" max="3" width="12.0" customWidth="true"/>
+    <col min="3" max="3" width="10.0" customWidth="true"/>
     <col min="4" max="4" width="9.0" customWidth="true"/>
-    <col min="5" max="5" width="10.0" customWidth="true"/>
+    <col min="5" max="5" width="8.0" customWidth="true"/>
     <col min="6" max="6" width="9.0" customWidth="true"/>
     <col min="7" max="7" width="8.0" customWidth="true"/>
-    <col min="8" max="8" width="9.0" customWidth="true"/>
-    <col min="9" max="9" width="8.0" customWidth="true"/>
+    <col min="8" max="8" width="10.0" customWidth="true"/>
+    <col min="9" max="9" width="12.0" customWidth="true"/>
+    <col min="10" max="10" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s" s="9">
         <v>24</v>
       </c>
-      <c r="D1" t="s" s="10">
+      <c r="D1" t="s" s="9">
         <v>25</v>
       </c>
       <c r="E1" t="s" s="9">
@@ -12527,13 +14291,16 @@
         <v>27</v>
       </c>
       <c r="G1" t="s" s="9">
+        <v>35</v>
+      </c>
+      <c r="H1" t="s" s="9">
         <v>28</v>
       </c>
-      <c r="H1" t="s" s="9">
+      <c r="I1" t="s" s="9">
         <v>29</v>
       </c>
-      <c r="I1" t="s" s="9">
-        <v>34</v>
+      <c r="J1" t="s" s="9">
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -12564,6 +14331,9 @@
       <c r="I2" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J2" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="s">
@@ -12593,6 +14363,9 @@
       <c r="I3" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J3" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="s">
@@ -12622,6 +14395,9 @@
       <c r="I4" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J4" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="s">
@@ -12651,6 +14427,9 @@
       <c r="I5" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J5" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="s">
@@ -12680,6 +14459,9 @@
       <c r="I6" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J6" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="s">
@@ -12709,6 +14491,9 @@
       <c r="I7" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J7" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="s">
@@ -12738,6 +14523,9 @@
       <c r="I8" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J8" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="s">
@@ -12767,6 +14555,9 @@
       <c r="I9" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J9" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
@@ -12796,6 +14587,9 @@
       <c r="I10" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J10" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="s">
@@ -12825,6 +14619,9 @@
       <c r="I11" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J11" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="s">
@@ -12854,6 +14651,9 @@
       <c r="I12" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J12" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="s">
@@ -12883,6 +14683,9 @@
       <c r="I13" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J13" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="s">
@@ -12912,6 +14715,9 @@
       <c r="I14" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J14" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="s">
@@ -12941,6 +14747,9 @@
       <c r="I15" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J15" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="s">
@@ -12970,6 +14779,9 @@
       <c r="I16" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J16" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
@@ -12999,6 +14811,9 @@
       <c r="I17" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J17" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
@@ -13028,6 +14843,9 @@
       <c r="I18" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J18" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="s">
@@ -13057,6 +14875,9 @@
       <c r="I19" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J19" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="s">
@@ -13086,6 +14907,9 @@
       <c r="I20" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J20" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="s">
@@ -13115,6 +14939,9 @@
       <c r="I21" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J21" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="s">
@@ -13144,6 +14971,9 @@
       <c r="I22" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J22" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="s">
@@ -13173,6 +15003,9 @@
       <c r="I23" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J23" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="s">
@@ -13202,6 +15035,9 @@
       <c r="I24" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J24" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="s">
@@ -13231,6 +15067,9 @@
       <c r="I25" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J25" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="s">
@@ -13260,6 +15099,9 @@
       <c r="I26" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J26" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="s">
@@ -13289,6 +15131,9 @@
       <c r="I27" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J27" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="s">
@@ -13318,6 +15163,9 @@
       <c r="I28" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J28" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="s">
@@ -13347,6 +15195,9 @@
       <c r="I29" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J29" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="s">
@@ -13376,6 +15227,9 @@
       <c r="I30" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J30" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="s">
@@ -13405,6 +15259,9 @@
       <c r="I31" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J31" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="s">
@@ -13434,6 +15291,9 @@
       <c r="I32" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J32" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="s">
@@ -13463,6 +15323,9 @@
       <c r="I33" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J33" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="s">
@@ -13492,6 +15355,9 @@
       <c r="I34" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J34" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="s">
@@ -13521,6 +15387,9 @@
       <c r="I35" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J35" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="s">
@@ -13550,6 +15419,9 @@
       <c r="I36" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J36" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="s">
@@ -13579,6 +15451,9 @@
       <c r="I37" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J37" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="s">
@@ -13608,6 +15483,9 @@
       <c r="I38" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J38" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="s">
@@ -13637,6 +15515,9 @@
       <c r="I39" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J39" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="s">
@@ -13666,6 +15547,9 @@
       <c r="I40" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J40" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="s">
@@ -13695,6 +15579,9 @@
       <c r="I41" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J41" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="s">
@@ -13724,6 +15611,9 @@
       <c r="I42" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J42" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="s">
@@ -13753,6 +15643,9 @@
       <c r="I43" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J43" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="s">
@@ -13782,6 +15675,9 @@
       <c r="I44" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J44" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="s">
@@ -13811,6 +15707,9 @@
       <c r="I45" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J45" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="s">
@@ -13840,6 +15739,9 @@
       <c r="I46" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J46" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="s">
@@ -13869,6 +15771,9 @@
       <c r="I47" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J47" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="s">
@@ -13898,6 +15803,9 @@
       <c r="I48" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J48" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="s">
@@ -13927,6 +15835,9 @@
       <c r="I49" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J49" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="s">
@@ -13956,6 +15867,9 @@
       <c r="I50" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J50" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="s">
@@ -13985,6 +15899,9 @@
       <c r="I51" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J51" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="s">
@@ -14014,6 +15931,9 @@
       <c r="I52" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J52" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="s">
@@ -14043,6 +15963,9 @@
       <c r="I53" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J53" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="s">
@@ -14072,6 +15995,9 @@
       <c r="I54" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J54" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="s">
@@ -14101,6 +16027,9 @@
       <c r="I55" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J55" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="s">
@@ -14130,6 +16059,9 @@
       <c r="I56" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J56" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="s">
@@ -14159,6 +16091,9 @@
       <c r="I57" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J57" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="s">
@@ -14188,6 +16123,9 @@
       <c r="I58" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J58" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="s">
@@ -14217,6 +16155,9 @@
       <c r="I59" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J59" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="s">
@@ -14246,6 +16187,9 @@
       <c r="I60" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J60" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="s">
@@ -14275,6 +16219,9 @@
       <c r="I61" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J61" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="s">
@@ -14304,6 +16251,9 @@
       <c r="I62" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J62" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="s">
@@ -14333,6 +16283,9 @@
       <c r="I63" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J63" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="s">
@@ -14362,6 +16315,9 @@
       <c r="I64" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J64" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="s">
@@ -14391,6 +16347,9 @@
       <c r="I65" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J65" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="11" t="s">
@@ -14420,6 +16379,9 @@
       <c r="I66" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J66" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="s">
@@ -14449,6 +16411,9 @@
       <c r="I67" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J67" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="11" t="s">
@@ -14478,6 +16443,9 @@
       <c r="I68" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J68" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="11" t="s">
@@ -14507,6 +16475,9 @@
       <c r="I69" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J69" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="s">
@@ -14536,6 +16507,9 @@
       <c r="I70" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J70" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="s">
@@ -14565,6 +16539,9 @@
       <c r="I71" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J71" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="s">
@@ -14594,6 +16571,9 @@
       <c r="I72" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J72" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="s">
@@ -14623,6 +16603,9 @@
       <c r="I73" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J73" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="11" t="s">
@@ -14652,6 +16635,9 @@
       <c r="I74" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J74" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="s">
@@ -14681,6 +16667,9 @@
       <c r="I75" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J75" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="11" t="s">
@@ -14710,6 +16699,9 @@
       <c r="I76" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J76" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="s">
@@ -14739,6 +16731,9 @@
       <c r="I77" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J77" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="11" t="s">
@@ -14768,6 +16763,9 @@
       <c r="I78" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J78" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="s">
@@ -14797,6 +16795,9 @@
       <c r="I79" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J79" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="11" t="s">
@@ -14826,6 +16827,9 @@
       <c r="I80" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J80" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="s">
@@ -14855,6 +16859,9 @@
       <c r="I81" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J81" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="s">
@@ -14884,6 +16891,9 @@
       <c r="I82" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J82" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="s">
@@ -14913,6 +16923,9 @@
       <c r="I83" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J83" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="s">
@@ -14942,6 +16955,9 @@
       <c r="I84" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J84" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="s">
@@ -14971,6 +16987,9 @@
       <c r="I85" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J85" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="s">
@@ -15000,6 +17019,9 @@
       <c r="I86" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J86" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="s">
@@ -15029,6 +17051,9 @@
       <c r="I87" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J87" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="s">
@@ -15058,6 +17083,9 @@
       <c r="I88" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J88" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="11" t="s">
@@ -15087,6 +17115,9 @@
       <c r="I89" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J89" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="11" t="s">
@@ -15116,6 +17147,9 @@
       <c r="I90" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J90" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="s">
@@ -15145,6 +17179,9 @@
       <c r="I91" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J91" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="s">
@@ -15174,6 +17211,9 @@
       <c r="I92" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J92" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="s">
@@ -15203,6 +17243,9 @@
       <c r="I93" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J93" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="s">
@@ -15232,6 +17275,9 @@
       <c r="I94" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J94" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="s">
@@ -15261,6 +17307,9 @@
       <c r="I95" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J95" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="s">
@@ -15290,6 +17339,9 @@
       <c r="I96" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J96" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="s">
@@ -15319,6 +17371,9 @@
       <c r="I97" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J97" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="s">
@@ -15348,6 +17403,9 @@
       <c r="I98" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J98" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="s">
@@ -15377,6 +17435,9 @@
       <c r="I99" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J99" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="s">
@@ -15406,6 +17467,9 @@
       <c r="I100" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J100" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="s">
@@ -15435,10 +17499,13 @@
       <c r="I101" s="11" t="s">
         <v>3</v>
       </c>
+      <c r="J101" s="11" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="H2:H101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="F2:F101" allowBlank="true" errorStyle="stop">
       <formula1>"公开,内部,秘密,机密"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15453,75 +17520,75 @@
   <cols>
     <col min="1" max="1" width="11.0" customWidth="true"/>
     <col min="2" max="2" width="11.0" customWidth="true"/>
-    <col min="3" max="3" width="14.0" customWidth="true"/>
-    <col min="4" max="4" width="13.0" customWidth="true"/>
-    <col min="5" max="5" width="11.0" customWidth="true"/>
-    <col min="6" max="6" width="10.0" customWidth="true"/>
-    <col min="7" max="7" width="10.0" customWidth="true"/>
-    <col min="8" max="8" width="11.0" customWidth="true"/>
-    <col min="9" max="9" width="11.0" customWidth="true"/>
+    <col min="3" max="3" width="11.0" customWidth="true"/>
+    <col min="4" max="4" width="10.0" customWidth="true"/>
+    <col min="5" max="5" width="10.0" customWidth="true"/>
+    <col min="6" max="6" width="11.0" customWidth="true"/>
+    <col min="7" max="7" width="11.0" customWidth="true"/>
+    <col min="8" max="8" width="10.0" customWidth="true"/>
+    <col min="9" max="9" width="8.0" customWidth="true"/>
     <col min="10" max="10" width="10.0" customWidth="true"/>
-    <col min="11" max="11" width="8.0" customWidth="true"/>
-    <col min="12" max="12" width="10.0" customWidth="true"/>
+    <col min="11" max="11" width="9.0" customWidth="true"/>
+    <col min="12" max="12" width="9.0" customWidth="true"/>
     <col min="13" max="13" width="9.0" customWidth="true"/>
-    <col min="14" max="14" width="9.0" customWidth="true"/>
-    <col min="15" max="15" width="9.0" customWidth="true"/>
-    <col min="16" max="16" width="13.0" customWidth="true"/>
-    <col min="17" max="17" width="12.0" customWidth="true"/>
+    <col min="14" max="14" width="13.0" customWidth="true"/>
+    <col min="15" max="15" width="12.0" customWidth="true"/>
+    <col min="16" max="16" width="14.0" customWidth="true"/>
+    <col min="17" max="17" width="13.0" customWidth="true"/>
     <col min="18" max="18" width="10.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s" s="12">
-        <v>36</v>
-      </c>
-      <c r="C1" t="s" s="13">
         <v>37</v>
       </c>
-      <c r="D1" t="s" s="13">
+      <c r="C1" t="s" s="12">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s" s="12">
         <v>38</v>
       </c>
       <c r="E1" t="s" s="12">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s" s="12">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s" s="12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s" s="12">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s" s="12">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s" s="12">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s" s="12">
         <v>44</v>
       </c>
       <c r="L1" t="s" s="12">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="M1" t="s" s="12">
-        <v>45</v>
-      </c>
-      <c r="N1" t="s" s="12">
         <v>46</v>
       </c>
-      <c r="O1" t="s" s="12">
+      <c r="N1" t="s" s="13">
         <v>47</v>
       </c>
+      <c r="O1" t="s" s="13">
+        <v>48</v>
+      </c>
       <c r="P1" t="s" s="13">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q1" t="s" s="13">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R1" t="s" s="12">
         <v>23</v>
@@ -21129,13 +23196,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="I2:I101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="G2:G101" allowBlank="true" errorStyle="stop">
       <formula1>"原材料,辅助材料,零部件,配套件,设备备件"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="H2:H101" allowBlank="true" errorStyle="stop">
       <formula1>"自制件,外购件,自制+外购"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="J2:J101" allowBlank="true" errorStyle="stop">
       <formula1>"个"</formula1>
     </dataValidation>
   </dataValidations>
@@ -21145,7 +23212,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.0" customWidth="true"/>
@@ -21153,13 +23220,11 @@
     <col min="3" max="3" width="10.0" customWidth="true"/>
     <col min="4" max="4" width="11.0" customWidth="true"/>
     <col min="5" max="5" width="10.0" customWidth="true"/>
-    <col min="6" max="6" width="12.0" customWidth="true"/>
+    <col min="6" max="6" width="10.0" customWidth="true"/>
     <col min="7" max="7" width="9.0" customWidth="true"/>
-    <col min="8" max="8" width="10.0" customWidth="true"/>
+    <col min="8" max="8" width="8.0" customWidth="true"/>
     <col min="9" max="9" width="9.0" customWidth="true"/>
-    <col min="10" max="10" width="8.0" customWidth="true"/>
-    <col min="11" max="11" width="9.0" customWidth="true"/>
-    <col min="12" max="12" width="11.0" customWidth="true"/>
+    <col min="10" max="10" width="11.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
@@ -21167,21 +23232,21 @@
         <v>4</v>
       </c>
       <c r="B1" t="s" s="15">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s" s="15">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s" s="16">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E1" t="s" s="16">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F1" t="s" s="15">
         <v>24</v>
       </c>
-      <c r="G1" t="s" s="16">
+      <c r="G1" t="s" s="15">
         <v>25</v>
       </c>
       <c r="H1" t="s" s="15">
@@ -21190,14 +23255,8 @@
       <c r="I1" t="s" s="15">
         <v>27</v>
       </c>
-      <c r="J1" t="s" s="15">
-        <v>28</v>
-      </c>
-      <c r="K1" t="s" s="15">
-        <v>29</v>
-      </c>
-      <c r="L1" t="s" s="16">
-        <v>54</v>
+      <c r="J1" t="s" s="16">
+        <v>55</v>
       </c>
     </row>
     <row r="2">
@@ -21231,12 +23290,6 @@
       <c r="J2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
@@ -21269,12 +23322,6 @@
       <c r="J3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="s">
@@ -21307,12 +23354,6 @@
       <c r="J4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
@@ -21345,12 +23386,6 @@
       <c r="J5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
@@ -21383,12 +23418,6 @@
       <c r="J6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K6" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
@@ -21421,12 +23450,6 @@
       <c r="J7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
@@ -21459,12 +23482,6 @@
       <c r="J8" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
@@ -21497,12 +23514,6 @@
       <c r="J9" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="s">
@@ -21535,12 +23546,6 @@
       <c r="J10" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
@@ -21573,12 +23578,6 @@
       <c r="J11" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K11" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L11" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="s">
@@ -21611,12 +23610,6 @@
       <c r="J12" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="s">
@@ -21649,12 +23642,6 @@
       <c r="J13" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K13" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="s">
@@ -21687,12 +23674,6 @@
       <c r="J14" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="s">
@@ -21725,12 +23706,6 @@
       <c r="J15" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="s">
@@ -21763,12 +23738,6 @@
       <c r="J16" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K16" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L16" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="17" t="s">
@@ -21801,12 +23770,6 @@
       <c r="J17" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="s">
@@ -21839,12 +23802,6 @@
       <c r="J18" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="s">
@@ -21877,12 +23834,6 @@
       <c r="J19" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K19" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L19" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="s">
@@ -21915,12 +23866,6 @@
       <c r="J20" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="s">
@@ -21953,12 +23898,6 @@
       <c r="J21" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="s">
@@ -21991,12 +23930,6 @@
       <c r="J22" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="s">
@@ -22029,12 +23962,6 @@
       <c r="J23" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="s">
@@ -22067,12 +23994,6 @@
       <c r="J24" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="s">
@@ -22105,12 +24026,6 @@
       <c r="J25" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L25" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="s">
@@ -22143,12 +24058,6 @@
       <c r="J26" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="s">
@@ -22181,12 +24090,6 @@
       <c r="J27" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="s">
@@ -22219,12 +24122,6 @@
       <c r="J28" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K28" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L28" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="s">
@@ -22257,12 +24154,6 @@
       <c r="J29" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="s">
@@ -22295,12 +24186,6 @@
       <c r="J30" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K30" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L30" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="s">
@@ -22333,12 +24218,6 @@
       <c r="J31" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K31" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L31" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="s">
@@ -22371,12 +24250,6 @@
       <c r="J32" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="s">
@@ -22409,12 +24282,6 @@
       <c r="J33" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="s">
@@ -22447,12 +24314,6 @@
       <c r="J34" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K34" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L34" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="s">
@@ -22485,12 +24346,6 @@
       <c r="J35" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="s">
@@ -22523,12 +24378,6 @@
       <c r="J36" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K36" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L36" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="s">
@@ -22561,12 +24410,6 @@
       <c r="J37" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K37" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L37" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="s">
@@ -22599,12 +24442,6 @@
       <c r="J38" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="s">
@@ -22637,12 +24474,6 @@
       <c r="J39" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K39" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L39" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="s">
@@ -22675,12 +24506,6 @@
       <c r="J40" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K40" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L40" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="17" t="s">
@@ -22713,12 +24538,6 @@
       <c r="J41" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="s">
@@ -22751,12 +24570,6 @@
       <c r="J42" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="s">
@@ -22789,12 +24602,6 @@
       <c r="J43" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="s">
@@ -22827,12 +24634,6 @@
       <c r="J44" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="s">
@@ -22865,12 +24666,6 @@
       <c r="J45" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="s">
@@ -22903,12 +24698,6 @@
       <c r="J46" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="s">
@@ -22941,12 +24730,6 @@
       <c r="J47" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="s">
@@ -22979,12 +24762,6 @@
       <c r="J48" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="s">
@@ -23017,12 +24794,6 @@
       <c r="J49" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="s">
@@ -23055,12 +24826,6 @@
       <c r="J50" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K50" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L50" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="s">
@@ -23093,12 +24858,6 @@
       <c r="J51" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K51" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L51" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="s">
@@ -23131,12 +24890,6 @@
       <c r="J52" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="s">
@@ -23169,12 +24922,6 @@
       <c r="J53" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K53" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L53" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="s">
@@ -23207,12 +24954,6 @@
       <c r="J54" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="s">
@@ -23245,12 +24986,6 @@
       <c r="J55" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K55" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L55" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="s">
@@ -23283,12 +25018,6 @@
       <c r="J56" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K56" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L56" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="s">
@@ -23321,12 +25050,6 @@
       <c r="J57" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="s">
@@ -23359,12 +25082,6 @@
       <c r="J58" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="s">
@@ -23397,12 +25114,6 @@
       <c r="J59" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="s">
@@ -23435,12 +25146,6 @@
       <c r="J60" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="17" t="s">
@@ -23473,12 +25178,6 @@
       <c r="J61" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K61" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L61" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="17" t="s">
@@ -23511,12 +25210,6 @@
       <c r="J62" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="17" t="s">
@@ -23549,12 +25242,6 @@
       <c r="J63" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K63" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L63" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="17" t="s">
@@ -23587,12 +25274,6 @@
       <c r="J64" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K64" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L64" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="17" t="s">
@@ -23625,12 +25306,6 @@
       <c r="J65" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K65" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L65" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="17" t="s">
@@ -23663,12 +25338,6 @@
       <c r="J66" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="17" t="s">
@@ -23701,12 +25370,6 @@
       <c r="J67" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K67" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L67" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="17" t="s">
@@ -23739,12 +25402,6 @@
       <c r="J68" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K68" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L68" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="s">
@@ -23777,12 +25434,6 @@
       <c r="J69" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K69" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L69" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="17" t="s">
@@ -23815,12 +25466,6 @@
       <c r="J70" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K70" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L70" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="17" t="s">
@@ -23853,12 +25498,6 @@
       <c r="J71" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K71" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L71" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="17" t="s">
@@ -23891,12 +25530,6 @@
       <c r="J72" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="17" t="s">
@@ -23929,12 +25562,6 @@
       <c r="J73" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K73" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L73" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="17" t="s">
@@ -23967,12 +25594,6 @@
       <c r="J74" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K74" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L74" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="s">
@@ -24005,12 +25626,6 @@
       <c r="J75" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K75" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L75" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="17" t="s">
@@ -24043,12 +25658,6 @@
       <c r="J76" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="17" t="s">
@@ -24081,12 +25690,6 @@
       <c r="J77" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K77" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L77" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="17" t="s">
@@ -24119,12 +25722,6 @@
       <c r="J78" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K78" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L78" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="17" t="s">
@@ -24157,12 +25754,6 @@
       <c r="J79" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K79" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L79" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="17" t="s">
@@ -24195,12 +25786,6 @@
       <c r="J80" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="17" t="s">
@@ -24233,12 +25818,6 @@
       <c r="J81" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="17" t="s">
@@ -24271,12 +25850,6 @@
       <c r="J82" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K82" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L82" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="17" t="s">
@@ -24309,12 +25882,6 @@
       <c r="J83" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="17" t="s">
@@ -24347,12 +25914,6 @@
       <c r="J84" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K84" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L84" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="17" t="s">
@@ -24385,12 +25946,6 @@
       <c r="J85" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K85" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L85" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="17" t="s">
@@ -24423,12 +25978,6 @@
       <c r="J86" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K86" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L86" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="17" t="s">
@@ -24461,12 +26010,6 @@
       <c r="J87" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K87" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L87" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="17" t="s">
@@ -24499,12 +26042,6 @@
       <c r="J88" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K88" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L88" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="17" t="s">
@@ -24537,12 +26074,6 @@
       <c r="J89" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="17" t="s">
@@ -24575,12 +26106,6 @@
       <c r="J90" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K90" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L90" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="17" t="s">
@@ -24613,12 +26138,6 @@
       <c r="J91" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="17" t="s">
@@ -24651,12 +26170,6 @@
       <c r="J92" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K92" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L92" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="17" t="s">
@@ -24689,12 +26202,6 @@
       <c r="J93" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K93" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L93" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="17" t="s">
@@ -24727,12 +26234,6 @@
       <c r="J94" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="17" t="s">
@@ -24765,12 +26266,6 @@
       <c r="J95" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K95" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L95" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="17" t="s">
@@ -24803,12 +26298,6 @@
       <c r="J96" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L96" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="17" t="s">
@@ -24841,12 +26330,6 @@
       <c r="J97" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K97" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L97" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="17" t="s">
@@ -24879,12 +26362,6 @@
       <c r="J98" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K98" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L98" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="s">
@@ -24917,12 +26394,6 @@
       <c r="J99" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K99" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L99" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="17" t="s">
@@ -24955,12 +26426,6 @@
       <c r="J100" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="17" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="17" t="s">
@@ -24991,12 +26456,6 @@
         <v>3</v>
       </c>
       <c r="J101" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="17" t="s">
         <v>3</v>
       </c>
     </row>
@@ -25008,7 +26467,7 @@
     <dataValidation type="list" sqref="C2:C101" allowBlank="true" errorStyle="stop">
       <formula1>"机加,装配,热表,铸造,钣焊,锻造,通用"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K2:K101" allowBlank="true" errorStyle="stop">
+    <dataValidation type="list" sqref="I2:I101" allowBlank="true" errorStyle="stop">
       <formula1>"公开,内部,秘密,机密"</formula1>
     </dataValidation>
   </dataValidations>
@@ -25042,55 +26501,55 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="18">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" t="s" s="18">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s" s="18">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s" s="19">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s" s="19">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" t="s" s="19">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" t="s" s="19">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" t="s" s="18">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" t="s" s="18">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J1" t="s" s="18">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K1" t="s" s="18">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L1" t="s" s="18">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M1" t="s" s="19">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N1" t="s" s="19">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O1" t="s" s="18">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P1" t="s" s="18">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q1" t="s" s="18">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
@@ -30426,19 +31885,19 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="21">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s" s="21">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s" s="21">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s" s="22">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" t="s" s="22">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2">
@@ -32166,22 +33625,22 @@
   <sheetData>
     <row r="1" ht="20.0" customHeight="true">
       <c r="A1" t="s" s="25">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s" s="25">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s" s="25">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s" s="25">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s" s="24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" t="s" s="24">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
